--- a/26-Modeling/002-Code/问题四/问题四结果.xlsx
+++ b/26-Modeling/002-Code/问题四/问题四结果.xlsx
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.373871684525827</v>
+        <v>2.712613812493025</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -1068,10 +1068,10 @@
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0.43</v>
@@ -1358,7 +1358,7 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -1371,16 +1371,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0.469</v>
@@ -1409,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
@@ -1425,7 +1425,7 @@
         <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -1476,7 +1476,7 @@
         <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -1524,16 +1524,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>0.399</v>
@@ -1562,7 +1562,7 @@
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
@@ -1578,7 +1578,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>18</v>
@@ -1629,7 +1629,7 @@
         <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>18</v>
@@ -1680,7 +1680,7 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>20</v>
@@ -1731,7 +1731,7 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>21</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>24</v>
@@ -1820,20 +1820,20 @@
         <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{U1,U3} | {U2,U4,U5}</t>
+          <t>{U1,U4,U5} | {U2,U3}</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>25</v>
@@ -1842,18 +1842,18 @@
         <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.173</v>
+        <v>0.21</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>67%/33%</t>
+          <t>71%/29%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>3</v>
@@ -1877,34 +1877,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>{U1,U4,U5} | {U2,U3}</t>
+          <t>{U1,U3} | {U2,U4,U5}</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.21</v>
+        <v>0.173</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>71%/29%</t>
+          <t>67%/33%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>3</v>
@@ -1919,10 +1919,10 @@
         <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1932,16 +1932,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" t="n">
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
         <v>0.28</v>
@@ -1970,7 +1970,7 @@
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>5</v>
@@ -1986,13 +1986,13 @@
         <v>43</v>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
         <v>0.179</v>
@@ -2021,10 +2021,10 @@
         <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2037,13 +2037,13 @@
         <v>44</v>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
         <v>0.249</v>
@@ -2072,10 +2072,10 @@
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2176,16 +2176,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>0.5659999999999999</v>
@@ -2214,7 +2214,7 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -2230,7 +2230,7 @@
         <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>18</v>
@@ -2281,7 +2281,7 @@
         <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>18</v>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>18</v>
@@ -2370,7 +2370,7 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>25</v>
@@ -2421,7 +2421,7 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>25</v>
@@ -2472,7 +2472,7 @@
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2485,7 +2485,7 @@
         <v>41</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>27</v>
@@ -2533,16 +2533,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
         <v>0.302</v>
@@ -2574,7 +2574,7 @@
         <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -2584,16 +2584,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>0.34</v>
@@ -2625,20 +2625,20 @@
         <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{U1} | {U2,U4,U5} | {U3}</t>
+          <t>{U1} | {U2,U3} | {U4,U5}</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
         <v>31</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60%/33%/7%</t>
+          <t>60%/29%/11%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2661,7 +2661,7 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
@@ -2673,23 +2673,23 @@
         <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>{U1} | {U2,U3} | {U4,U5}</t>
+          <t>{U1} | {U2,U4,U5} | {U3}</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>43</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>31</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>60%/29%/11%</t>
+          <t>60%/33%/7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2712,7 +2712,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
@@ -2724,7 +2724,7 @@
         <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -2740,7 +2740,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
         <v>31</v>
@@ -2784,11 +2784,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>{U1,U3} | {U2} | {U4,U5}</t>
+          <t>{U1,U4,U5} | {U2} | {U3}</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="n">
         <v>16</v>
@@ -2800,21 +2800,21 @@
         <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.34</v>
+        <v>0.377</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>67%/22%/11%</t>
+          <t>71%/22%/7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>9</v>
@@ -2826,23 +2826,23 @@
         <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>{U1,U3,U4} | {U2} | {U5}</t>
+          <t>{U1,U3} | {U2} | {U4,U5}</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>44</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
         <v>32</v>
@@ -2851,11 +2851,11 @@
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>70%/22%/8%</t>
+          <t>67%/22%/11%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2886,27 +2886,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>{U1} | {U2,U5} | {U3,U4}</t>
+          <t>{U1,U5} | {U2,U3} | {U4}</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>44</v>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>0.27</v>
+        <v>0.346</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>60%/30%/10%</t>
+          <t>68%/29%/3%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2916,13 +2916,13 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
@@ -2937,43 +2937,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>{U1} | {U2,U3,U4} | {U5}</t>
+          <t>{U1,U3,U4} | {U2} | {U5}</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>60%/32%/8%</t>
+          <t>70%/22%/8%</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
@@ -2982,49 +2982,49 @@
         <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>{U1,U4,U5} | {U2} | {U3}</t>
+          <t>{U1,U3,U5} | {U2} | {U4}</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="n">
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>0.377</v>
+        <v>0.416</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>71%/22%/7%</t>
+          <t>75%/22%/3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>9</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
         <v>5</v>
@@ -3033,20 +3033,20 @@
         <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>{U1,U5} | {U2,U3} | {U4}</t>
+          <t>{U1} | {U2,U5} | {U3,U4}</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
         <v>35</v>
@@ -3055,11 +3055,11 @@
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>0.346</v>
+        <v>0.27</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68%/29%/3%</t>
+          <t>60%/30%/10%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3069,35 +3069,35 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>8</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
         <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>{U1,U3} | {U2,U4} | {U5}</t>
+          <t>{U1} | {U2,U3,U4} | {U5}</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20" t="n">
         <v>36</v>
@@ -3106,11 +3106,11 @@
         <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67%/25%/8%</t>
+          <t>60%/32%/8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3123,7 +3123,7 @@
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
         <v>6</v>
@@ -3135,20 +3135,20 @@
         <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>{U1,U3,U5} | {U2} | {U4}</t>
+          <t>{U1,U5} | {U2,U4} | {U3}</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>46</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" t="n">
         <v>36</v>
@@ -3157,21 +3157,21 @@
         <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>0.416</v>
+        <v>0.346</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>75%/22%/3%</t>
+          <t>68%/25%/7%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
@@ -3183,7 +3183,7 @@
         <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
         <v>6</v>
@@ -3192,43 +3192,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>{U1} | {U2} | {U3,U4,U5}</t>
+          <t>{U1,U3} | {U2,U4} | {U5}</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>60%/22%/18%</t>
+          <t>67%/25%/8%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>9</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
@@ -3237,20 +3237,20 @@
         <v>5</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>{U1,U4} | {U2} | {U3,U5}</t>
+          <t>{U1} | {U2} | {U3,U4,U5}</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>46</v>
       </c>
       <c r="C23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
         <v>38</v>
@@ -3259,11 +3259,11 @@
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63%/22%/15%</t>
+          <t>60%/22%/18%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3294,27 +3294,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>{U1,U5} | {U2,U4} | {U3}</t>
+          <t>{U1,U4} | {U2} | {U3,U5}</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>46</v>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>0.346</v>
+        <v>0.3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>68%/25%/7%</t>
+          <t>63%/22%/15%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3330,7 +3330,7 @@
         <v>9</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
         <v>5</v>
@@ -3339,40 +3339,40 @@
         <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>{U1} | {U2,U4} | {U3,U5}</t>
+          <t>{U1,U5} | {U2} | {U3,U4}</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>47</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>0.27</v>
+        <v>0.346</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>60%/25%/15%</t>
+          <t>68%/22%/10%</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -3390,40 +3390,40 @@
         <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>{U1,U5} | {U2} | {U3,U4}</t>
+          <t>{U1} | {U2,U4} | {U3,U5}</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26" t="n">
-        <v>0.346</v>
+        <v>0.27</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>68%/22%/10%</t>
+          <t>60%/25%/15%</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>4</v>
@@ -3438,10 +3438,10 @@
         <v>5</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3622,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>3</v>
@@ -3748,7 +3748,7 @@
         <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
         <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
@@ -4073,7 +4073,7 @@
         <v>49.154</v>
       </c>
       <c r="J2" t="n">
-        <v>4.176</v>
+        <v>4.501</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -4103,7 +4103,7 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -4141,10 +4141,10 @@
         <v>27.251</v>
       </c>
       <c r="J3" t="n">
-        <v>3.519</v>
+        <v>4.967</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>2.819</v>
@@ -4201,10 +4201,10 @@
         <v>76.404</v>
       </c>
       <c r="J4" t="n">
-        <v>7.695</v>
+        <v>9.468</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -4229,7 +4229,7 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4352,7 +4352,7 @@
         <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
@@ -4394,10 +4394,10 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4551,7 +4551,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>4.641</v>
+        <v>4.967</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -4578,7 +4578,7 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
         <v>3</v>
@@ -4687,7 +4687,7 @@
         <v>1.825</v>
       </c>
       <c r="J4" t="n">
-        <v>0.416</v>
+        <v>1.173</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -4747,7 +4747,7 @@
         <v>76.404</v>
       </c>
       <c r="J5" t="n">
-        <v>5.057</v>
+        <v>6.14</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -4772,7 +4772,7 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>4</v>
@@ -4856,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
@@ -5097,7 +5097,7 @@
         <v>49.154</v>
       </c>
       <c r="J2" t="n">
-        <v>4.176</v>
+        <v>4.501</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -5127,7 +5127,7 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5138,46 +5138,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U2,U4,U5</t>
+          <t>U2,U3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S003、S007、S013、S014、S015</t>
+          <t>S003、S006、S007、S011、S015</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="H3" t="n">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="I3" t="n">
-        <v>22.071</v>
+        <v>21.35</v>
       </c>
       <c r="J3" t="n">
-        <v>3.519</v>
+        <v>3.328</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>2.819</v>
+        <v>2.433</v>
       </c>
       <c r="M3" t="n">
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -5186,16 +5186,16 @@
         <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -5206,64 +5206,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U4,U5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S006、S011</t>
+          <t>S013、S014</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>5.179</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
+        <v>1.639</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.423</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5293,10 +5293,10 @@
         <v>76.404</v>
       </c>
       <c r="J5" t="n">
-        <v>7.695</v>
+        <v>9.468</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -5306,7 +5306,7 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>8</v>
@@ -5318,10 +5318,10 @@
         <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -5390,7 +5390,7 @@
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -5402,7 +5402,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
@@ -5474,7 +5474,7 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
@@ -5486,10 +5486,10 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5594,10 +5594,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -5618,7 +5618,7 @@
         <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -5640,10 +5640,10 @@
         <v>0.43</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>5</v>
@@ -5664,7 +5664,7 @@
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>3</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>0.103</v>
@@ -5713,7 +5713,7 @@
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -5732,10 +5732,10 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
@@ -5756,7 +5756,7 @@
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
         <v>0.27</v>
@@ -5790,7 +5790,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>8</v>
@@ -5802,10 +5802,10 @@
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5819,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5963,32 +5963,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K=2</t>
+          <t>K=3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中继机</t>
+          <t>运输机A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>G1 峰值 3 @ 2.31 h；G2 峰值 0 @ 0.00 h</t>
+          <t>G1 峰值 4 @ 0.36 h；G2 峰值 1 @ 0.00 h；G3 峰值 0 @ 0.00 h</t>
         </is>
       </c>
     </row>
@@ -6000,17 +6000,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>运输机A</t>
+          <t>运输机B</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>G1 峰值 4 @ 0.36 h；G2 峰值 1 @ 0.00 h；G3 峰值 0 @ 0.00 h</t>
+          <t>G1 峰值 2 @ 1.12 h；G2 峰值 0 @ 0.00 h；G3 峰值 1 @ 0.70 h</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>运输机B</t>
+          <t>运输机C</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>G1 峰值 2 @ 1.12 h；G2 峰值 0 @ 0.00 h；G3 峰值 1 @ 0.70 h</t>
+          <t>G1 峰值 2 @ 0.00 h；G2 峰值 1 @ 0.84 h；G3 峰值 0 @ 0.00 h</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>运输机C</t>
+          <t>电池A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>G1 峰值 2 @ 0.00 h；G2 峰值 1 @ 0.84 h；G3 峰值 0 @ 0.00 h</t>
+          <t>G1 峰值 6 @ 0.61 h；G2 峰值 1 @ 0.00 h；G3 峰值 0 @ 0.00 h</t>
         </is>
       </c>
     </row>
@@ -6096,17 +6096,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>电池A</t>
+          <t>电池B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>G1 峰值 6 @ 0.61 h；G2 峰值 1 @ 0.00 h；G3 峰值 0 @ 0.00 h</t>
+          <t>G1 峰值 4 @ 1.52 h；G2 峰值 0 @ 0.00 h；G3 峰值 1 @ 0.70 h</t>
         </is>
       </c>
     </row>
@@ -6128,17 +6128,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>电池B</t>
+          <t>中继机</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -6148,39 +6148,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>G1 峰值 4 @ 1.52 h；G2 峰值 0 @ 0.00 h；G3 峰值 1 @ 0.70 h</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>K=3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>中继机</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>G1 峰值 3 @ 2.31 h；G2 峰值 0 @ 0.00 h；G3 峰值 1 @ 0.70 h</t>
+          <t>G1 峰值 2 @ 0.17 h；G2 峰值 0 @ 0.00 h；G3 峰值 1 @ 0.02 h</t>
         </is>
       </c>
     </row>

--- a/26-Modeling/002-Code/问题四/问题四结果.xlsx
+++ b/26-Modeling/002-Code/问题四/问题四结果.xlsx
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,7 +740,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K=2 G1 平移后中继资源</t>
+          <t>K=2 G1 平移后通信连续覆盖</t>
         </is>
       </c>
       <c r="B10" t="b">
@@ -751,33 +751,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K=2 G2 平移后硬时限</t>
+          <t>K=2 G1 平移后中继能量</t>
         </is>
       </c>
       <c r="B11" t="b">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4 箱</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K=2 G2 完成时间限制</t>
+          <t>K=2 G2 平移后硬时限</t>
         </is>
       </c>
       <c r="B12" t="b">
         <v>1</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4 箱</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K=2 G2 平移后中继资源</t>
+          <t>K=2 G2 完成时间限制</t>
         </is>
       </c>
       <c r="B13" t="b">
@@ -788,7 +788,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K=3 每个服务区仅一组</t>
+          <t>K=2 G2 平移后通信连续覆盖</t>
         </is>
       </c>
       <c r="B14" t="b">
@@ -799,7 +799,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K=3 每个架次仅一组</t>
+          <t>K=2 G2 平移后中继能量</t>
         </is>
       </c>
       <c r="B15" t="b">
@@ -810,7 +810,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K=3 多点架次不拆分</t>
+          <t>K=3 每个服务区仅一组</t>
         </is>
       </c>
       <c r="B16" t="b">
@@ -821,7 +821,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K=3 资源泳道数等于峰值</t>
+          <t>K=3 每个架次仅一组</t>
         </is>
       </c>
       <c r="B17" t="b">
@@ -832,22 +832,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K=3 中继需求区间全覆盖</t>
+          <t>K=3 多点架次不拆分</t>
         </is>
       </c>
       <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>75 个需求窗按组分配</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K=3 中继能量与返航余量</t>
+          <t>K=3 资源泳道数等于峰值</t>
         </is>
       </c>
       <c r="B19" t="b">
@@ -858,7 +854,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K=3 G1 平移后硬时限</t>
+          <t>K=3 中继需求区间全覆盖</t>
         </is>
       </c>
       <c r="B20" t="b">
@@ -866,14 +862,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>25 箱</t>
+          <t>75 个需求窗按组分配</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K=3 G1 完成时间限制</t>
+          <t>K=3 中继能量与返航余量</t>
         </is>
       </c>
       <c r="B21" t="b">
@@ -884,33 +880,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K=3 G1 平移后中继资源</t>
+          <t>K=3 G1 平移后硬时限</t>
         </is>
       </c>
       <c r="B22" t="b">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>25 箱</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K=3 G2 平移后硬时限</t>
+          <t>K=3 G1 完成时间限制</t>
         </is>
       </c>
       <c r="B23" t="b">
         <v>1</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4 箱</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K=3 G2 完成时间限制</t>
+          <t>K=3 G1 平移后通信连续覆盖</t>
         </is>
       </c>
       <c r="B24" t="b">
@@ -921,7 +917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K=3 G2 平移后中继资源</t>
+          <t>K=3 G1 平移后中继能量</t>
         </is>
       </c>
       <c r="B25" t="b">
@@ -932,7 +928,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K=3 G3 平移后硬时限</t>
+          <t>K=3 G2 平移后硬时限</t>
         </is>
       </c>
       <c r="B26" t="b">
@@ -940,14 +936,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2 箱</t>
+          <t>4 箱</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>K=3 G3 完成时间限制</t>
+          <t>K=3 G2 完成时间限制</t>
         </is>
       </c>
       <c r="B27" t="b">
@@ -958,13 +954,72 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K=3 G3 平移后中继资源</t>
+          <t>K=3 G2 平移后通信连续覆盖</t>
         </is>
       </c>
       <c r="B28" t="b">
         <v>1</v>
       </c>
       <c r="C28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>K=3 G2 平移后中继能量</t>
+        </is>
+      </c>
+      <c r="B29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>K=3 G3 平移后硬时限</t>
+        </is>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2 箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>K=3 G3 完成时间限制</t>
+        </is>
+      </c>
+      <c r="B31" t="b">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>K=3 G3 平移后通信连续覆盖</t>
+        </is>
+      </c>
+      <c r="B32" t="b">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>K=3 G3 平移后中继能量</t>
+        </is>
+      </c>
+      <c r="B33" t="b">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
